--- a/data/trans_orig/P1801_2016_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1801_2016_2023-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>93840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132153</t>
+          <t>129939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140226</t>
+          <t>143024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>180427</t>
+          <t>182536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244804</t>
+          <t>244803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299473</t>
+          <t>299736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287310</t>
+          <t>289524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>324816</t>
+          <t>325623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215328</t>
+          <t>213219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255529</t>
+          <t>252731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515745</t>
+          <t>515482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570414</t>
+          <t>570415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155460</t>
+          <t>158520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200496</t>
+          <t>202843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>254701</t>
+          <t>253774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300397</t>
+          <t>301325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>425079</t>
+          <t>426075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>491125</t>
+          <t>490718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>387653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435036</t>
+          <t>431976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263147</t>
+          <t>262219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308843</t>
+          <t>309770</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>662915</t>
+          <t>663322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728961</t>
+          <t>727965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,08%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>253723</t>
+          <t>256084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305552</t>
+          <t>306821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>319057</t>
+          <t>320800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>371180</t>
+          <t>371162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>588508</t>
+          <t>590633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>663208</t>
+          <t>661660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>363545</t>
+          <t>362276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415374</t>
+          <t>413013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290206</t>
+          <t>290224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>342329</t>
+          <t>340586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667275</t>
+          <t>668823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>741975</t>
+          <t>739850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>287057</t>
+          <t>283664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>338843</t>
+          <t>338225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310805</t>
+          <t>311776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>363324</t>
+          <t>363118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>611455</t>
+          <t>610484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>689822</t>
+          <t>688492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307205</t>
+          <t>307823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358991</t>
+          <t>362384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285753</t>
+          <t>285959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>338272</t>
+          <t>337301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>605303</t>
+          <t>606633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683670</t>
+          <t>684641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254395</t>
+          <t>254006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>298243</t>
+          <t>298054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>308439</t>
+          <t>307425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>350108</t>
+          <t>353336</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>573580</t>
+          <t>571678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>638298</t>
+          <t>637852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179675</t>
+          <t>179864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>223523</t>
+          <t>223912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146741</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188410</t>
+          <t>189424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>336469</t>
+          <t>336915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401187</t>
+          <t>403089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>208993</t>
+          <t>208045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>244647</t>
+          <t>242862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>269249</t>
+          <t>266494</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>302161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>486545</t>
+          <t>486665</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>537142</t>
+          <t>534071</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89683</t>
+          <t>91468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125337</t>
+          <t>126285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74134</t>
+          <t>75601</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108513</t>
+          <t>111268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>174950</t>
+          <t>178021</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>225547</t>
+          <t>225427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181364</t>
+          <t>182225</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205769</t>
+          <t>206098</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>265038</t>
+          <t>265821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>308824</t>
+          <t>305412</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>457817</t>
+          <t>456155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>504079</t>
+          <t>504362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51229</t>
+          <t>50900</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75634</t>
+          <t>74773</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>91345</t>
+          <t>94757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135131</t>
+          <t>134348</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>153088</t>
+          <t>152805</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>199350</t>
+          <t>201012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1517483</t>
+          <t>1524395</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1638137</t>
+          <t>1638978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1966592</t>
+          <t>1962823</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2083332</t>
+          <t>2088270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3512610</t>
+          <t>3525518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3685006</t>
+          <t>3700078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1756213</t>
+          <t>1755372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1876867</t>
+          <t>1869955</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1461210</t>
+          <t>1456272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1577950</t>
+          <t>1581719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3253886</t>
+          <t>3238814</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3426282</t>
+          <t>3413374</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>76541</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57183</t>
+          <t>54506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117111</t>
+          <t>104568</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>127197</t>
+          <t>146401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106435</t>
+          <t>121093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>150463</t>
+          <t>171944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>212500</t>
+          <t>222942</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175073</t>
+          <t>187733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249649</t>
+          <t>260442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>314683</t>
+          <t>331252</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282876</t>
+          <t>303225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>342804</t>
+          <t>353287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>185840</t>
+          <t>214446</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162574</t>
+          <t>188903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206602</t>
+          <t>239754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>500524</t>
+          <t>545698</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463375</t>
+          <t>508198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537951</t>
+          <t>580907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313037</t>
+          <t>360847</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313037</t>
+          <t>360847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313037</t>
+          <t>360847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713024</t>
+          <t>768640</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713024</t>
+          <t>768640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713024</t>
+          <t>768640</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>146652</t>
+          <t>162004</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122194</t>
+          <t>135251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172824</t>
+          <t>190468</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>190446</t>
+          <t>208576</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119305</t>
+          <t>184894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228426</t>
+          <t>232171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>337098</t>
+          <t>370580</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255861</t>
+          <t>332647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379672</t>
+          <t>406656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>276895</t>
+          <t>314886</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250723</t>
+          <t>286422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>301353</t>
+          <t>341639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>320137</t>
+          <t>291618</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>282157</t>
+          <t>268023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>391278</t>
+          <t>315300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>597032</t>
+          <t>606504</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554458</t>
+          <t>570428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>678269</t>
+          <t>644437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510583</t>
+          <t>500194</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510583</t>
+          <t>500194</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510583</t>
+          <t>500194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934130</t>
+          <t>977084</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934130</t>
+          <t>977084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934130</t>
+          <t>977084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>233496</t>
+          <t>255022</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>209357</t>
+          <t>231028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256454</t>
+          <t>281716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>259564</t>
+          <t>297277</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>239117</t>
+          <t>276623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>276902</t>
+          <t>319558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>493060</t>
+          <t>552299</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>464080</t>
+          <t>516798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>524398</t>
+          <t>584079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>301561</t>
+          <t>364736</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278603</t>
+          <t>338042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325700</t>
+          <t>388730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>282223</t>
+          <t>324199</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>264885</t>
+          <t>301918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302670</t>
+          <t>344853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>583784</t>
+          <t>688936</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>552446</t>
+          <t>657156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>612764</t>
+          <t>724437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541787</t>
+          <t>621476</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541787</t>
+          <t>621476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541787</t>
+          <t>621476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076844</t>
+          <t>1241235</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076844</t>
+          <t>1241235</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076844</t>
+          <t>1241235</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>589579</t>
+          <t>363770</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>464298</t>
+          <t>337958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>758791</t>
+          <t>388485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>386843</t>
+          <t>417529</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>325250</t>
+          <t>394469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>416475</t>
+          <t>439039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>976423</t>
+          <t>781299</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>846211</t>
+          <t>747073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1229204</t>
+          <t>816654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>297164</t>
+          <t>335720</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127952</t>
+          <t>311005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>422445</t>
+          <t>361532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>324737</t>
+          <t>318017</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295105</t>
+          <t>296507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386330</t>
+          <t>341077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>621900</t>
+          <t>653737</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369119</t>
+          <t>618382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>752112</t>
+          <t>687963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886743</t>
+          <t>699490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886743</t>
+          <t>699490</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886743</t>
+          <t>699490</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711580</t>
+          <t>735546</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711580</t>
+          <t>735546</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711580</t>
+          <t>735546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598323</t>
+          <t>1435036</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598323</t>
+          <t>1435036</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598323</t>
+          <t>1435036</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>324262</t>
+          <t>345188</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>300612</t>
+          <t>321105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>346379</t>
+          <t>369255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>349035</t>
+          <t>390847</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>332327</t>
+          <t>373473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>365297</t>
+          <t>408589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>673297</t>
+          <t>736035</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>644367</t>
+          <t>708403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>703794</t>
+          <t>766155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>235981</t>
+          <t>263088</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213864</t>
+          <t>239021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>259631</t>
+          <t>287171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>197573</t>
+          <t>216649</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181311</t>
+          <t>198907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214281</t>
+          <t>234023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>433554</t>
+          <t>479737</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>403057</t>
+          <t>449617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>462484</t>
+          <t>507369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560243</t>
+          <t>608276</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560243</t>
+          <t>608276</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560243</t>
+          <t>608276</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546608</t>
+          <t>607496</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546608</t>
+          <t>607496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546608</t>
+          <t>607496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106851</t>
+          <t>1215772</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106851</t>
+          <t>1215772</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106851</t>
+          <t>1215772</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>239096</t>
+          <t>262520</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>223688</t>
+          <t>247706</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>251961</t>
+          <t>280327</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>473547</t>
+          <t>293417</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>398028</t>
+          <t>278854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>553819</t>
+          <t>308036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>712643</t>
+          <t>555937</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>635323</t>
+          <t>533271</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>836325</t>
+          <t>577915</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>129069</t>
+          <t>144560</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116204</t>
+          <t>126753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>144477</t>
+          <t>159374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>134414</t>
+          <t>145317</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>130698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209933</t>
+          <t>159880</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>263484</t>
+          <t>289877</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>139802</t>
+          <t>267899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340804</t>
+          <t>312543</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607961</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607961</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607961</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976127</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976127</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976127</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>208433</t>
+          <t>226615</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>195401</t>
+          <t>211881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220491</t>
+          <t>239264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>301622</t>
+          <t>330518</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>287382</t>
+          <t>314251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>314042</t>
+          <t>343377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>510055</t>
+          <t>557133</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>489406</t>
+          <t>538368</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>528048</t>
+          <t>576014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>74326</t>
+          <t>83583</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62268</t>
+          <t>70934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87358</t>
+          <t>98317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>123127</t>
+          <t>132957</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110707</t>
+          <t>120098</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137367</t>
+          <t>149224</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>197453</t>
+          <t>216540</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>179460</t>
+          <t>197659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218102</t>
+          <t>235305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424749</t>
+          <t>463475</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424749</t>
+          <t>463475</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424749</t>
+          <t>463475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707508</t>
+          <t>773673</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707508</t>
+          <t>773673</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707508</t>
+          <t>773673</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1826823</t>
+          <t>1691660</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1682575</t>
+          <t>1626326</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2227435</t>
+          <t>1757140</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2088253</t>
+          <t>2084564</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1952295</t>
+          <t>2026244</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2367460</t>
+          <t>2136118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3915075</t>
+          <t>3776224</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3688333</t>
+          <t>3695188</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4351924</t>
+          <t>3868475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1629678</t>
+          <t>1837826</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1229066</t>
+          <t>1772346</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1773926</t>
+          <t>1903160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1568052</t>
+          <t>1643204</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1288845</t>
+          <t>1591650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1704010</t>
+          <t>1701524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3197731</t>
+          <t>3481030</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2760882</t>
+          <t>3388779</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3424473</t>
+          <t>3562066</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
